--- a/research/traditional_assets/database/data/egypt/egypt_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_publishing_newspapers.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.201</v>
+        <v>-0.27</v>
       </c>
       <c r="G2">
-        <v>0.1153061224489796</v>
+        <v>-0.2613445378151261</v>
       </c>
       <c r="H2">
-        <v>0.1163265306122449</v>
+        <v>-0.2613445378151261</v>
       </c>
       <c r="I2">
-        <v>-0.2607142857142857</v>
+        <v>-0.3957983193277311</v>
       </c>
       <c r="J2">
-        <v>-0.2607142857142857</v>
+        <v>-0.3957983193277311</v>
       </c>
       <c r="K2">
-        <v>-0.717</v>
+        <v>-0.108</v>
       </c>
       <c r="L2">
-        <v>-0.3658163265306122</v>
+        <v>-0.0907563025210084</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="V2">
-        <v>0.005555555555555556</v>
+        <v>0.008715596330275228</v>
       </c>
       <c r="W2">
-        <v>-0.1475308641975308</v>
+        <v>-0.02596153846153846</v>
       </c>
       <c r="X2">
-        <v>0.1491512935269653</v>
+        <v>0.3221925222626109</v>
       </c>
       <c r="Y2">
-        <v>-0.2966821577244961</v>
+        <v>-0.3481540607241493</v>
       </c>
       <c r="Z2">
-        <v>0.2607076350093109</v>
+        <v>0.173545282193379</v>
       </c>
       <c r="AA2">
-        <v>-0.06797020484171322</v>
+        <v>-0.06868893101939623</v>
       </c>
       <c r="AB2">
-        <v>0.1129942023791546</v>
+        <v>0.1900554594773093</v>
       </c>
       <c r="AC2">
-        <v>-0.1809644072208679</v>
+        <v>-0.2587443904967056</v>
       </c>
       <c r="AD2">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="AG2">
-        <v>2.697</v>
+        <v>3.101</v>
       </c>
       <c r="AH2">
-        <v>0.3965014577259476</v>
+        <v>0.5886792452830188</v>
       </c>
       <c r="AI2">
-        <v>0.3953488372093023</v>
+        <v>0.5551601423487544</v>
       </c>
       <c r="AJ2">
-        <v>0.3944712593242651</v>
+        <v>0.5871993940541563</v>
       </c>
       <c r="AK2">
-        <v>0.3933206941811287</v>
+        <v>0.5536511337261203</v>
       </c>
       <c r="AL2">
-        <v>0.28</v>
+        <v>0.206</v>
       </c>
       <c r="AM2">
-        <v>0.279</v>
+        <v>0.206</v>
       </c>
       <c r="AN2">
-        <v>-11.87772925764192</v>
+        <v>-7.306791569086651</v>
       </c>
       <c r="AO2">
-        <v>-1.825</v>
+        <v>-2.286407766990291</v>
       </c>
       <c r="AP2">
-        <v>-11.77729257641921</v>
+        <v>-7.262295081967213</v>
       </c>
       <c r="AQ2">
-        <v>-1.831541218637993</v>
+        <v>-2.286407766990291</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.201</v>
+        <v>-0.27</v>
       </c>
       <c r="G3">
-        <v>0.1153061224489796</v>
+        <v>-0.2613445378151261</v>
       </c>
       <c r="H3">
-        <v>0.1163265306122449</v>
+        <v>-0.2613445378151261</v>
       </c>
       <c r="I3">
-        <v>-0.2607142857142857</v>
+        <v>-0.3957983193277311</v>
       </c>
       <c r="J3">
-        <v>-0.2607142857142857</v>
+        <v>-0.3957983193277311</v>
       </c>
       <c r="K3">
-        <v>-0.717</v>
+        <v>-0.108</v>
       </c>
       <c r="L3">
-        <v>-0.3658163265306122</v>
+        <v>-0.0907563025210084</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="V3">
-        <v>0.005555555555555556</v>
+        <v>0.008715596330275228</v>
       </c>
       <c r="W3">
-        <v>-0.1475308641975308</v>
+        <v>-0.02596153846153846</v>
       </c>
       <c r="X3">
-        <v>0.1491512935269653</v>
+        <v>0.3221925222626109</v>
       </c>
       <c r="Y3">
-        <v>-0.2966821577244961</v>
+        <v>-0.3481540607241493</v>
       </c>
       <c r="Z3">
-        <v>0.2607076350093109</v>
+        <v>0.173545282193379</v>
       </c>
       <c r="AA3">
-        <v>-0.06797020484171322</v>
+        <v>-0.06868893101939623</v>
       </c>
       <c r="AB3">
-        <v>0.1129942023791546</v>
+        <v>0.1900554594773093</v>
       </c>
       <c r="AC3">
-        <v>-0.1809644072208679</v>
+        <v>-0.2587443904967056</v>
       </c>
       <c r="AD3">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="AG3">
-        <v>2.697</v>
+        <v>3.101</v>
       </c>
       <c r="AH3">
-        <v>0.3965014577259476</v>
+        <v>0.5886792452830188</v>
       </c>
       <c r="AI3">
-        <v>0.3953488372093023</v>
+        <v>0.5551601423487544</v>
       </c>
       <c r="AJ3">
-        <v>0.3944712593242651</v>
+        <v>0.5871993940541563</v>
       </c>
       <c r="AK3">
-        <v>0.3933206941811287</v>
+        <v>0.5536511337261203</v>
       </c>
       <c r="AL3">
-        <v>0.28</v>
+        <v>0.206</v>
       </c>
       <c r="AM3">
-        <v>0.279</v>
+        <v>0.206</v>
       </c>
       <c r="AN3">
-        <v>-11.87772925764192</v>
+        <v>-7.306791569086651</v>
       </c>
       <c r="AO3">
-        <v>-1.825</v>
+        <v>-2.286407766990291</v>
       </c>
       <c r="AP3">
-        <v>-11.77729257641921</v>
+        <v>-7.262295081967213</v>
       </c>
       <c r="AQ3">
-        <v>-1.831541218637993</v>
+        <v>-2.286407766990291</v>
       </c>
     </row>
   </sheetData>
